--- a/excel/data.xlsx
+++ b/excel/data.xlsx
@@ -474,7 +474,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Percentage</t>
+          <t>Additional Value</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -576,20 +576,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>單點質感焙果系列送薯餅</t>
+          <t>單點勁辣鷄腿堡+$38元飲品特價$99(原價$116起)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3200</v>
+        <v>3400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TW Buy One Get One Or Another Discounted(Percentage)</t>
+          <t>TW Price Deal - Two Product Sets - Reduced Price</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Buy Bagel series Get Hash Browns</t>
+          <t>Spicy Chicken Filet Burger+ $38 beverage $99 (original price starting from $116)​</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -599,12 +599,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Buy Bagel series Get Hash Browns</t>
+          <t>Spicy Chicken Filet Burger+ $38 beverage $99 (original price starting from $116)​</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>單點質感焙果系列送薯餅</t>
+          <t>單點勁辣鷄腿堡+$38元飲品特價$99(原價$116起)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -614,22 +614,22 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>單點質感焙果系列送薯餅</t>
+          <t>單點勁辣鷄腿堡+$38元飲品特價$99(原價$116起)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2432|2433|2434|67405</t>
+          <t>31373</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>67405</t>
+          <t>3184|3189|3194|33414|3035</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>67,32</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Buy Bagel series Get Hash Browns</t>
+          <t>Spicy Chicken Filet Burger+ $38 beverage $99 (original price starting from $116)​</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>單點質感焙果系列送薯餅</t>
+          <t>單點勁辣鷄腿堡+$38元飲品特價$99(原價$116起)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -674,82 +674,90 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>10:30 AM</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>5:00 AM</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>10:30 AM</t>
-        </is>
-      </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Chicken (Sandwiches &amp; Wraps)</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Each offer may be redeemed once only. Multiple offers or rewards of different items may be used in a single transaction.</t>
+          <t>Each offer may be redeemed once only. ​</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>- Please refer to the app for the actual redemption method. This offer does not apply to McDelivery advance orders and certain restaurants.
-- Registration and login are required for use. Mobile phone screenshots are invalid.
-- Multiple offers or rewards of different items may be used in a single transaction. Actual redemption is subject to the products displayed in McDonald’s restaurant system at the time of purchase.
-- Each offer may only be redeemed once per device and becomes invalid after redemption. Switching accounts on the same device to redeem an offer is not permitted.
-- This offer is for personal use only. Mobile phone screenshots or copied images are not valid for redemption.
-- This offer has an expiration date. Valid until the date shown on the voucher. Please redeem by 11:59 PM or before the meal’s service time ends on the expiration date.
-- Any unused offer after the expiration date will be deemed as forfeited, and it cannot be returned or be exchanged for cash or another product at the same price.
-- Once redeemed, this offer is considered used. For refund, it cannot be returned or redeemed items cannot be changed.
-- Redemption is limited to the items listed on this offer. It cannot be exchanged or redeemed for cash.
-- Images are for reference only. The products’ serving times and flavors are based on the actual availability at each McDonald’s restaurant. Quantities are limited, and while stocks last.
+          <t>- $38 beverage includes medium-sized soda drinks (Coca-Cola, Coca-Cola zero, Sprite), medium-sized Lemon Flavored Black Tea (Iced) and Tea (Hot). It cannot be upgraded to other beverages with an additonal charge.​
+- Please refer to the app for the actual redemption method. This offer does not apply to McDelivery advance orders and certain restaurants.​
+- Offers apply independently. When multiple Offers are used in the same transaction, each Offer’s conditions and qualifying threshold must be met separately; Offers may not be combined or double-counted.​
+- Registration and login are required for use. Mobile phone screenshots are invalid.​
+- Actual redemption is subject to the products displayed in McDonald’s restaurant system at the time of purchase.​
+- Each offer may only be redeemed once per device and becomes invalid after redemption. Switching accounts on the same device to redeem an offer is not permitted.​
+- This offer is for personal use only. Mobile phone screenshots or copied images are not valid for redemption.​
+- This offer has an expiration date. Valid until the date shown on the voucher. Please redeem by 11:59 PM or before the meal’s service time ends on the expiration date.​
+- Any unused offer after the expiration date will be deemed as forfeited, and it cannot be returned or be exchanged for cash or another product at the same price.​
+- Once redeemed, this offer is considered used. For refund, it cannot be returned or redeemed items cannot be changed.​
+- Redemption is limited to the items listed on this offer. It cannot be exchanged or redeemed for cash.​
+- Images are for reference only. The products’ serving times and flavors are based on the actual availability at each McDonald’s restaurant. Quantities are limited, and while stocks last.​
 - McDonald's reserves the right to interpret, adjust the event rules, event timing, event content, promotional policies, and to terminate the event at any time without prior notice.</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>每券限兌換一次。每筆交易可以同時使用多張不同品項之回饋券或優惠券。</t>
+          <t>每券限兌換一次。​</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>- 兌換方式依券面顯示為準，不適用歡樂送預約訂餐及部分餐廳
-- 註冊並登入方可使用，手機截圖無效
-- 每筆交易可以同時使用多張不同品項之回饋券或優惠券，每券每裝置限兌換一次，無法使用同一個裝置切換帳號使用，實際兌換請以當下餐廳系統顯示為準
-- 使用效期依券面所示，請於到期當日 23:59 前或餐點供應時段結束前使用完畢，逾期未使用視同放棄，恕無法要求返還，亦不得要求更換等值商品或現金
-- 本券經兌換視為已使用，退貨恕無法要求返還或變更兌換之贈品品項
-- 優惠產品以本券內項目為限，不得要求更換、兌換現金使用
-- 圖片僅供參考，供應時間及口味，以各麥當勞餐廳實際供應為準，數量有限，售(送)完為止
+          <t>- 38元飲品包含中杯汽水類飲品(可口可樂、可口可樂zero、雪碧)及中杯檸檬風味紅茶(冰)及紅茶(熱)，不可補差額升級其他飲品​
+- 兌換方式依券面顯示為準，不適用歡樂送預約訂餐及部分餐廳​
+- 每張優惠券獨立適用；同時使用多張優惠券時，須分別滿足各張優惠券之使用條件，且各優惠券之使用門檻須獨立計算，不得合併或重複使用​
+- 註冊並登入方可使用，手機截圖無效​
+- 每券每裝置限兌換一次，無法使用同一個裝置切換帳號使用，實際兌換請以當下餐廳系統顯示為準​
+- 使用效期依券面所示，請於到期當日 23:59 前或餐點供應時段結束前使用完畢，逾期未使用視同放棄，恕無法要求返還，亦不得要求更換等值商品或現金​
+- 本券經兌換視為已使用，退貨恕無法要求返還或變更兌換之贈品品項​
+- 優惠產品以本券內項目為限，不得要求更換、兌換現金使用​
+- 圖片僅供參考，供應時間及口味，以各麥當勞餐廳實際供應為準，數量有限，售(送)完為止​
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>dealFilter6Breakfast 早餐</t>
+          <t>Segment &gt; Pen_Segment_1,Segment &gt; test</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7,Deal Filter Tag &gt; dealFilter9</t>
+        </is>
+      </c>
       <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>單點豐盛鬆餅系列送薯餅</t>
+          <t>麥香魚+$38飲品特價$79 (原價$90起)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TW Buy One Get One Or Another Discounted(Percentage)</t>
+          <t>TW Price Deal - Two Product Sets - Reduced Price</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Buy Hotcakes series Get Hash Browns</t>
+          <t>fish Filet Burger+ $38 beverage $99 (original price starting from $116)​</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -759,12 +767,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buy Hotcakes series Get Hash Browns</t>
+          <t>fish Filet Burger+ $38 beverage $99 (original price starting from $116)​</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>單點豐盛鬆餅系列送薯餅</t>
+          <t>麥香魚+$38飲品特價$79 (原價$90起)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -774,22 +782,22 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>單點豐盛鬆餅系列送薯餅</t>
+          <t>麥香魚+$38飲品特價$79 (原價$90起)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2072|2112|2113|2073|67405</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>67405</t>
+          <t>1239|3184|3189|3194|33414|3035</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>46,33</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -804,12 +812,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Buy Hotcakes series Get Hash Browns</t>
+          <t>fish Filet Burger+ $38 beverage $99 (original price starting from $116)​</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>單點豐盛鬆餅系列送薯餅</t>
+          <t>麥香魚+$38飲品特價$79 (原價$90起)</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -834,69 +842,77 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>5:00 AM</t>
+          <t>Nan</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>10:30 AM</t>
+          <t>Nan</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Fish</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Each offer may be redeemed once only. Multiple offers or rewards of different items may be used in a single transaction.</t>
+          <t>Each offer may be redeemed once only. ​</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>- Please refer to the app for the actual redemption method. This offer does not apply to McDelivery advance orders and certain restaurants.
-- Registration and login are required for use. Mobile phone screenshots are invalid.
-- Multiple offers or rewards of different items may be used in a single transaction. Actual redemption is subject to the products displayed in McDonald’s restaurant system at the time of purchase.
-- Each offer may only be redeemed once per device and becomes invalid after redemption. Switching accounts on the same device to redeem an offer is not permitted.
-- This offer is for personal use only. Mobile phone screenshots or copied images are not valid for redemption.
-- This offer has an expiration date. Valid until the date shown on the voucher. Please redeem by 11:59 PM or before the meal’s service time ends on the expiration date.
-- Any unused offer after the expiration date will be deemed as forfeited, and it cannot be returned or be exchanged for cash or another product at the same price.
-- Once redeemed, this offer is considered used. For refund, it cannot be returned or redeemed items cannot be changed.
-- Redemption is limited to the items listed on this offer. It cannot be exchanged or redeemed for cash.
-- Images are for reference only. The products’ serving times and flavors are based on the actual availability at each McDonald’s restaurant. Quantities are limited, and while stocks last.
+          <t>- $38 beverage includes medium-sized soda drinks (Coca-Cola, Coca-Cola zero, Sprite), medium-sized Lemon Flavored Black Tea (Iced) and Tea (Hot). It cannot be upgraded to other beverages with an additonal charge.​
+- Please refer to the app for the actual redemption method. This offer does not apply to McDelivery advance orders and certain restaurants.​
+- Offers apply independently. When multiple Offers are used in the same transaction, each Offer’s conditions and qualifying threshold must be met separately; Offers may not be combined or double-counted.​
+- Registration and login are required for use. Mobile phone screenshots are invalid.​
+- Actual redemption is subject to the products displayed in McDonald’s restaurant system at the time of purchase.​
+- Each offer may only be redeemed once per device and becomes invalid after redemption. Switching accounts on the same device to redeem an offer is not permitted.​
+- This offer is for personal use only. Mobile phone screenshots or copied images are not valid for redemption.​
+- This offer has an expiration date. Valid until the date shown on the voucher. Please redeem by 11:59 PM or before the meal’s service time ends on the expiration date.​
+- Any unused offer after the expiration date will be deemed as forfeited, and it cannot be returned or be exchanged for cash or another product at the same price.​
+- Once redeemed, this offer is considered used. For refund, it cannot be returned or redeemed items cannot be changed.​
+- Redemption is limited to the items listed on this offer. It cannot be exchanged or redeemed for cash.​
+- Images are for reference only. The products’ serving times and flavors are based on the actual availability at each McDonald’s restaurant. Quantities are limited, and while stocks last.​
 - McDonald's reserves the right to interpret, adjust the event rules, event timing, event content, promotional policies, and to terminate the event at any time without prior notice.</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>每券限兌換一次。每筆交易可以同時使用多張不同品項之回饋券或優惠券。</t>
+          <t>每券限兌換一次。​</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>- 兌換方式依券面顯示為準，不適用歡樂送預約訂餐及部分餐廳
-- 註冊並登入方可使用，手機截圖無效
-- 每筆交易可以同時使用多張不同品項之回饋券或優惠券，每券每裝置限兌換一次，無法使用同一個裝置切換帳號使用，實際兌換請以當下餐廳系統顯示為準
-- 使用效期依券面所示，請於到期當日 23:59 前或餐點供應時段結束前使用完畢，逾期未使用視同放棄，恕無法要求返還，亦不得要求更換等值商品或現金
-- 本券經兌換視為已使用，退貨恕無法要求返還或變更兌換之贈品品項
-- 優惠產品以本券內項目為限，不得要求更換、兌換現金使用
-- 圖片僅供參考，供應時間及口味，以各麥當勞餐廳實際供應為準，數量有限，售(送)完為止
+          <t>- 38元飲品包含中杯汽水類飲品(可口可樂、可口可樂zero、雪碧)及中杯檸檬風味紅茶(冰)及紅茶(熱)，不可補差額升級其他飲品​
+- 兌換方式依券面顯示為準，不適用歡樂送預約訂餐及部分餐廳​
+- 每張優惠券獨立適用；同時使用多張優惠券時，須分別滿足各張優惠券之使用條件，且各優惠券之使用門檻須獨立計算，不得合併或重複使用​
+- 註冊並登入方可使用，手機截圖無效​
+- 每券每裝置限兌換一次，無法使用同一個裝置切換帳號使用，實際兌換請以當下餐廳系統顯示為準​
+- 使用效期依券面所示，請於到期當日 23:59 前或餐點供應時段結束前使用完畢，逾期未使用視同放棄，恕無法要求返還，亦不得要求更換等值商品或現金​
+- 本券經兌換視為已使用，退貨恕無法要求返還或變更兌換之贈品品項​
+- 優惠產品以本券內項目為限，不得要求更換、兌換現金使用​
+- 圖片僅供參考，供應時間及口味，以各麥當勞餐廳實際供應為準，數量有限，售(送)完為止​
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>dealFilter6Breakfast 早餐</t>
+          <t>Segment &gt; Pen_Segment_1</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter9</t>
+        </is>
+      </c>
       <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>買指定超值全餐送4塊咖哩辣味麥克鷄塊</t>
+          <t>(10) 麥香魚+中薯+$38中飲特價$99</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -904,7 +920,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TW Buy One Get One Or Another Discounted(Percentage)</t>
+          <t>TW Price Deal - Three Product Sets - Reduced Price</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -924,7 +940,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>買指定超值全餐送4塊咖哩辣味麥克鷄塊</t>
+          <t>(10) 麥香魚+中薯+$38中飲特價$99</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -934,22 +950,22 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>買指定超值全餐送4塊咖哩辣味麥克鷄塊</t>
+          <t>(10) 麥香魚+中薯+$38中飲特價$99</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>37460|37455|67219|67880|37461|47742|37463|47460|47461|37459|46911|67881|47482|67329|67330|67241|67242|67331|67615|67616|67617|67614|67737|67714|67749|67726|67735|67712|67750|67727|67733|67710|67746|67723|67740|67717|67736|67713|67745|67722|67738|67715|67741|67718|67742|67719|67734|67711|67739|67716|67744|67721|67747|67724|67748|67725|67743|67720|67751|67728|67752|67729|67753|67730|67754|67731|67755|67732|67427|67824|67825|67826|67827|67828|67829|67830|67831|67832|67833|67834|67835|67836|67837|67838|67839|67840|67841|67842|67843|67844|67845|47440|67088|67902|67903|67906|67907|68207|68208|68265</t>
+          <t>37460</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>68265</t>
+          <t>37455|67219|67880|37461|47742|37463|47460|47461|37459|46911|67881|47482|67329|67330|67241|67242|67331|67615|67616|67617|67614|67737|67714|67749|67726|67735|67712|67750|67727|67733|67710|67746|67723|67740|67717|67736|67713|67745|67722|67738|67715|67741|67718|67742|67719|67734|67711|67739|67716|67744|67721|67747|67724|67748|67725|67743|67720|67751|67728|67752|67729|67753|67730|67754|67731|67755|67732|67427|67824|67825|67826|67827|67828|67829|67830|67831|67832|67833|67834|67835|67836|67837|67838|67839|67840|67841|67842|67843|67844|67845|47440|67088|67902|67903|67906|67907|68207|68208|68265</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>24,36,28</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -969,7 +985,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>買指定超值全餐送4塊咖哩辣味麥克鷄塊</t>
+          <t>(10) 麥香魚+中薯+$38中飲特價$99</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1004,7 +1020,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Product preference 01 (LTO)</t>
+          <t>Product preference 01</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1052,17 +1068,21 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
+          <t>Segment &gt; Pen_Segment_1,Segment &gt; test</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR</t>
+        </is>
+      </c>
       <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>買指定超值全餐送小杯玉米湯</t>
+          <t>單點麥香鷄+4塊麥克鷄塊+小薯+小飲$101</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1070,7 +1090,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TW Buy One Get One Or Another Discounted(Percentage)</t>
+          <t>TW Price Deal - Four Product Sets - Reduced Price</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1090,7 +1110,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>買指定超值全餐送小杯玉米湯</t>
+          <t>單點麥香鷄+4塊麥克鷄塊+小薯+小飲$101</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1100,22 +1120,22 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>買指定超值全餐送小杯玉米湯</t>
+          <t>單點麥香鷄+4塊麥克鷄塊+小薯+小飲$101</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>37460|37455|67219|67880|37461|47742|37463|47460|47461|37459|46911|67881|47482|67329|67330|67241|67242|67331|67615|67616|67617|67614|67737|67714|67749|67726|67735|67712|67750|67727|67733|67710|67746|67723|67740|67717|67736|67713|67745|67722|67738|67715|67741|67718|67742|67719|67734|67711|67739|67716|67744|67721|67747|67724|67748|67725|67743|67720|67751|67728|67752|67729|67753|67730|67754|67731|67755|67732|67427|67824|67825|67826|67827|67828|67829|67830|67831|67832|67833|67834|67835|67836|67837|67838|67839|67840|67841|67842|67843|67844|67845|47440|67088|67902|67903|67906|67907|68207|68208|67409</t>
+          <t>37460</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>67409</t>
+          <t>37455|67219|67880|37461|47742|37463|47460|47461|37459|46911|67881|47482|67329|67330|67241|67242|67331|67615|67616|67617|67614|67737|67714|67749|67726|67735|67712|67750|67727|67733|67710|67746|67723|67740|67717|67736|67713|67745|67722|67738|67715|67741|67718|67742|67719|67734|67711|67739|67716|67744|67721|67747|67724|67748|67725|67743|67720|67751|67728|67752|67729|67753|67730|67754|67731|67755|67732|67427|67824|67825|67826|67827|67828|67829|67830|67831|67832|67833|67834|67835|67836|67837|67838|67839|67840|67841|67842|67843|67844|67845|47440|67088|67902|67903|67906|67907|68207|68208|67409</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>24,36,23,38</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1135,7 +1155,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>買指定超值全餐送小杯玉米湯</t>
+          <t>單點麥香鷄+4塊麥克鷄塊+小薯+小飲$101</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1212,19 +1232,19 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>買指定超值全餐送蛋捲冰淇淋</t>
+          <t>勁辣鷄腿堡+4塊麥克鷄塊+小薯+ICC+小飲 $159</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1232,7 +1252,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TW Buy One Get One Or Another Discounted(Percentage)</t>
+          <t>TW Price Deal - Five Product Sets - Reduced Price</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1252,7 +1272,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>買指定超值全餐送蛋捲冰淇淋</t>
+          <t>勁辣鷄腿堡+4塊麥克鷄塊+小薯+ICC+小飲 $159</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1262,22 +1282,22 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>買指定超值全餐送蛋捲冰淇淋</t>
+          <t>勁辣鷄腿堡+4塊麥克鷄塊+小薯+ICC+小飲 $159</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>37460|37455|67219|67880|37461|47742|37463|47460|47461|37459|46911|67881|47482|67329|67330|67241|67242|67331|67615|67616|67617|67614|67737|67714|67749|67726|67735|67712|67750|67727|67733|67710|67746|67723|67740|67717|67736|67713|67745|67722|67738|67715|67741|67718|67742|67719|67734|67711|67739|67716|67744|67721|67747|67724|67748|67725|67743|67720|67751|67728|67752|67729|67753|67730|67754|67731|67755|67732|67427|67824|67825|67826|67827|67828|67829|67830|67831|67832|67833|67834|67835|67836|67837|67838|67839|67840|67841|67842|67843|67844|67845|47440|67088|67902|67903|67906|67907|68207|68208|67406</t>
+          <t>37460</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>67406</t>
+          <t>37455|67219|67880|37461|47742|37463|47460|47461|37459|46911|67881|47482|67329|67330|67241|67242|67331|67615|67616|67617|67614|67737|67714|67749|67726|67735|67712|67750|67727|67733|67710|67746|67723|67740|67717|67736|67713|67745|67722|67738|67715|67741|67718|67742|67719|67734|67711|67739|67716|67744|67721|67747|67724|67748|67725|67743|67720|67751|67728|67752|67729|67753|67730|67754|67731|67755|67732|67427|67824|67825|67826|67827|67828|67829|67830|67831|67832|67833|67834|67835|67836|67837|67838|67839|67840|67841|67842|67843|67844|67845|47440|67088|67902|67903|67906|67907|68207|68208|67406</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>62,36,23,0,38</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1297,7 +1317,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>買指定超值全餐送蛋捲冰淇淋</t>
+          <t>勁辣鷄腿堡+4塊麥克鷄塊+小薯+ICC+小飲 $159</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1374,17 +1394,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>dealFilter8 Iced Desserts 冰品點心</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -1540,13 +1556,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>dealFilter9McCafe &amp; Drinks 咖啡飲品</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter9</t>
+        </is>
+      </c>
       <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1660,7 +1676,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Product preference 01 (LTO)</t>
+          <t>Product preference 01</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1704,13 +1720,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1824,7 +1840,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Product preference 01 (LTO)</t>
+          <t>Product preference 01</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1868,13 +1884,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1888,7 +1904,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MPA TW Discount Off Product(Percentage) Pre tax False</t>
+          <t>TW Buy One Get One Or Another Discounted(Percentage)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2027,17 +2043,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>dealFilter6Breakfast 早餐</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter6</t>
+        </is>
+      </c>
       <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -2190,17 +2202,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>dealFilter6Breakfast 早餐</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter6,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -2214,7 +2222,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MPA TW Discount Off Product(Percentage) Pre tax False</t>
+          <t>TW Buy One Get One Or Another Discounted(Percentage)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2357,7 +2365,11 @@
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR</t>
+        </is>
+      </c>
       <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -2512,13 +2524,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -2632,7 +2644,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Product preference 01 (LTO)</t>
+          <t>Product preference 01</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2682,13 +2694,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -2795,17 +2807,13 @@
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>dealFilter9McCafe &amp; Drinks 咖啡飲品</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter9</t>
+        </is>
+      </c>
       <c r="AE15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -2819,7 +2827,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MPA TW Discount Off Product(Percentage) Pre tax False</t>
+          <t>TW Buy One Get One Or Another Discounted(Percentage)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2962,7 +2970,11 @@
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR</t>
+        </is>
+      </c>
       <c r="AE16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -3116,13 +3128,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>dealFilter9McCafe &amp; Drinks 咖啡飲品</t>
-        </is>
-      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter9</t>
+        </is>
+      </c>
       <c r="AE17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -3277,13 +3289,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>dealFilter9McCafe &amp; Drinks 咖啡飲品</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter9</t>
+        </is>
+      </c>
       <c r="AE18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -3392,13 +3404,13 @@
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -3509,7 +3521,11 @@
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR</t>
+        </is>
+      </c>
       <c r="AE20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -3618,13 +3634,13 @@
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -3638,7 +3654,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MPA TW Discount Off Product(Percentage) Pre tax False</t>
+          <t>TW Buy One Get One Or Another Discounted(Percentage)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -3733,17 +3749,13 @@
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>dealFilter6Breakfast 早餐</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter6</t>
+        </is>
+      </c>
       <c r="AE22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -3852,17 +3864,13 @@
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>dealFilter6Breakfast 早餐</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter6,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -3971,13 +3979,13 @@
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
+      <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -4086,13 +4094,13 @@
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>dealFilter9McCafe &amp; Drinks 咖啡飲品</t>
-        </is>
-      </c>
+      <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter9</t>
+        </is>
+      </c>
       <c r="AE25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -4106,7 +4114,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MPA TW Discount Off Product(Percentage) Pre tax False</t>
+          <t>TW Buy One Get One Or Another Discounted(Percentage)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -4203,7 +4211,11 @@
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
-      <c r="AD26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR</t>
+        </is>
+      </c>
       <c r="AE26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -4217,7 +4229,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MPA TW Discount Off Product(Percentage) Pre tax False</t>
+          <t>TW Buy One Get One Or Another Discounted(Percentage)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -4314,7 +4326,11 @@
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR</t>
+        </is>
+      </c>
       <c r="AE27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -4423,17 +4439,13 @@
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>dealFilter8 Iced Desserts 冰品點心</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7,Deal Filter Tag &gt; dealFilter8</t>
+        </is>
+      </c>
       <c r="AE28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -4542,13 +4554,13 @@
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
+      <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -4657,13 +4669,13 @@
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -4774,7 +4786,11 @@
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR</t>
+        </is>
+      </c>
       <c r="AE31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -4883,13 +4899,13 @@
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
+      <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -4998,13 +5014,13 @@
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>dealFilter9McCafe &amp; Drinks 咖啡飲品</t>
-        </is>
-      </c>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter9</t>
+        </is>
+      </c>
       <c r="AE33" t="inlineStr"/>
     </row>
     <row r="34">
@@ -5018,7 +5034,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MPA TW Discount Off Product(Percentage) Pre tax False</t>
+          <t>TW Buy One Get One Or Another Discounted(Percentage)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5125,17 +5141,13 @@
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr"/>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>dealFilter6Breakfast 早餐</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter6</t>
+        </is>
+      </c>
       <c r="AE34" t="inlineStr"/>
     </row>
     <row r="35">
@@ -5256,17 +5268,13 @@
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>dealFilter6Breakfast 早餐</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter6,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -5387,13 +5395,13 @@
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>dealFilter9McCafe &amp; Drinks 咖啡飲品</t>
-        </is>
-      </c>
+      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter9</t>
+        </is>
+      </c>
       <c r="AE36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -5502,17 +5510,13 @@
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>dealFilter9McCafe &amp; Drinks 咖啡飲品</t>
-        </is>
-      </c>
-      <c r="AD37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7,Deal Filter Tag &gt; dealFilter9</t>
+        </is>
+      </c>
       <c r="AE37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -5635,7 +5639,11 @@
       <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr"/>
-      <c r="AD38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR</t>
+        </is>
+      </c>
       <c r="AE38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -5756,13 +5764,13 @@
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
+      <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr"/>
-      <c r="AD39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE39" t="inlineStr"/>
     </row>
     <row r="40">
@@ -5776,7 +5784,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MPA TW Discount Off Product(Percentage) Pre tax False</t>
+          <t>TW Buy One Get One Or Another Discounted(Percentage)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5883,17 +5891,13 @@
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr"/>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>dealFilter6Breakfast 早餐</t>
-        </is>
-      </c>
-      <c r="AD40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter6</t>
+        </is>
+      </c>
       <c r="AE40" t="inlineStr"/>
     </row>
     <row r="41">
@@ -6014,13 +6018,13 @@
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr"/>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
+      <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr"/>
-      <c r="AD41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -6141,13 +6145,13 @@
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
+      <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr"/>
-      <c r="AD42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE42" t="inlineStr"/>
     </row>
     <row r="43">
@@ -6268,17 +6272,13 @@
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr"/>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>dealFilter8 Iced Desserts 冰品點心</t>
-        </is>
-      </c>
-      <c r="AD43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7,Deal Filter Tag &gt; dealFilter8</t>
+        </is>
+      </c>
       <c r="AE43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -6399,13 +6399,13 @@
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr"/>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
+      <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr"/>
-      <c r="AD44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE44" t="inlineStr"/>
     </row>
     <row r="45">
@@ -6492,7 +6492,11 @@
       <c r="AA45" t="inlineStr"/>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr"/>
-      <c r="AD45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -6579,7 +6583,11 @@
       <c r="AA46" t="inlineStr"/>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr"/>
-      <c r="AD46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE46" t="inlineStr"/>
     </row>
     <row r="47">
@@ -6666,7 +6674,11 @@
       <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="inlineStr"/>
-      <c r="AD47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR</t>
+        </is>
+      </c>
       <c r="AE47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -6753,7 +6765,11 @@
       <c r="AA48" t="inlineStr"/>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="inlineStr"/>
-      <c r="AD48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter6</t>
+        </is>
+      </c>
       <c r="AE48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -6840,7 +6856,11 @@
       <c r="AA49" t="inlineStr"/>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr"/>
-      <c r="AD49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter8</t>
+        </is>
+      </c>
       <c r="AE49" t="inlineStr"/>
     </row>
     <row r="50">
@@ -6927,7 +6947,11 @@
       <c r="AA50" t="inlineStr"/>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr"/>
-      <c r="AD50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter9</t>
+        </is>
+      </c>
       <c r="AE50" t="inlineStr"/>
     </row>
     <row r="51">
@@ -7014,7 +7038,11 @@
       <c r="AA51" t="inlineStr"/>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="inlineStr"/>
-      <c r="AD51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE51" t="inlineStr"/>
     </row>
     <row r="52">
@@ -7101,7 +7129,11 @@
       <c r="AA52" t="inlineStr"/>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="inlineStr"/>
-      <c r="AD52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -7259,13 +7291,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
+      <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr"/>
-      <c r="AD53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -7423,13 +7455,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
+      <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="inlineStr"/>
-      <c r="AD54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE54" t="inlineStr"/>
     </row>
     <row r="55">
@@ -7443,7 +7475,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MPA TW Discount Off Product(Percentage) Pre tax False</t>
+          <t>TW Buy One Get One Or Another Discounted(Percentage)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7587,7 +7619,11 @@
       </c>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="inlineStr"/>
-      <c r="AD55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR</t>
+        </is>
+      </c>
       <c r="AE55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -7743,13 +7779,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>dealFilter9McCafe &amp; Drinks 咖啡飲品</t>
-        </is>
-      </c>
+      <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="inlineStr"/>
-      <c r="AD56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter9</t>
+        </is>
+      </c>
       <c r="AE56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -7763,7 +7799,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MPA TW Discount Off Product(Percentage) Pre tax False</t>
+          <t>TW Buy One Get One Or Another Discounted(Percentage)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7903,17 +7939,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>dealFilter6Breakfast 早餐</t>
-        </is>
-      </c>
-      <c r="AD57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter6</t>
+        </is>
+      </c>
       <c r="AE57" t="inlineStr"/>
     </row>
     <row r="58">
@@ -8067,17 +8099,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>dealFilter6Breakfast 早餐</t>
-        </is>
-      </c>
-      <c r="AD58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr"/>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter6,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE58" t="inlineStr"/>
     </row>
     <row r="59">
@@ -8231,13 +8259,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
+      <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="inlineStr"/>
-      <c r="AD59" t="inlineStr"/>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE59" t="inlineStr"/>
     </row>
     <row r="60">
@@ -8391,13 +8419,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
+      <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr"/>
-      <c r="AD60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -8552,17 +8580,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>dealFilter8 Iced Desserts 冰品點心</t>
-        </is>
-      </c>
-      <c r="AD61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7,Deal Filter Tag &gt; dealFilter8</t>
+        </is>
+      </c>
       <c r="AE61" t="inlineStr"/>
     </row>
     <row r="62">
@@ -8718,13 +8742,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>dealFilter9McCafe &amp; Drinks 咖啡飲品</t>
-        </is>
-      </c>
+      <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr"/>
-      <c r="AD62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter9</t>
+        </is>
+      </c>
       <c r="AE62" t="inlineStr"/>
     </row>
     <row r="63">
@@ -8878,13 +8902,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>dealFilter9McCafe &amp; Drinks 咖啡飲品</t>
-        </is>
-      </c>
+      <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="inlineStr"/>
-      <c r="AD63" t="inlineStr"/>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter9</t>
+        </is>
+      </c>
       <c r="AE63" t="inlineStr"/>
     </row>
     <row r="64">
@@ -8898,7 +8922,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MPA TW Discount Off Product(Percentage) Pre tax False</t>
+          <t>TW Buy One Get One Or Another Discounted(Percentage)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9038,17 +9062,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>dealFilter6Breakfast 早餐</t>
-        </is>
-      </c>
-      <c r="AD64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="inlineStr"/>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter6</t>
+        </is>
+      </c>
       <c r="AE64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -9204,13 +9224,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
+      <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="inlineStr"/>
-      <c r="AD65" t="inlineStr"/>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE65" t="inlineStr"/>
     </row>
     <row r="66">
@@ -9368,13 +9388,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
+      <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="inlineStr"/>
-      <c r="AD66" t="inlineStr"/>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE66" t="inlineStr"/>
     </row>
     <row r="67">
@@ -9534,17 +9554,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>dealFilter8 Iced Desserts 冰品點心</t>
-        </is>
-      </c>
-      <c r="AD67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="inlineStr"/>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE67" t="inlineStr"/>
     </row>
     <row r="68">
@@ -9558,7 +9574,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MPA TW Discount Off Product(Percentage) Pre tax False</t>
+          <t>TW Buy One Get One Or Another Discounted(Percentage)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9698,17 +9714,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>dealFilter6Breakfast 早餐</t>
-        </is>
-      </c>
-      <c r="AD68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr"/>
+      <c r="AC68" t="inlineStr"/>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter6</t>
+        </is>
+      </c>
       <c r="AE68" t="inlineStr"/>
     </row>
     <row r="69">
@@ -9866,13 +9878,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利​</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
+      <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr"/>
-      <c r="AD69" t="inlineStr"/>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE69" t="inlineStr"/>
     </row>
     <row r="70">
@@ -10032,17 +10044,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>dealFilter8 Iced Desserts 冰品點心</t>
-        </is>
-      </c>
-      <c r="AD70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr"/>
+      <c r="AC70" t="inlineStr"/>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE70" t="inlineStr"/>
     </row>
     <row r="71">
@@ -10195,7 +10203,11 @@
       </c>
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="inlineStr"/>
-      <c r="AD71" t="inlineStr"/>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR</t>
+        </is>
+      </c>
       <c r="AE71" t="inlineStr"/>
     </row>
     <row r="72">
@@ -10292,17 +10304,13 @@
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr"/>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>dealFilter9McCafe &amp; Drinks 咖啡飲品</t>
-        </is>
-      </c>
-      <c r="AD72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="inlineStr"/>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7,Deal Filter Tag &gt; dealFilter9</t>
+        </is>
+      </c>
       <c r="AE72" t="inlineStr"/>
     </row>
     <row r="73">
@@ -10399,17 +10407,13 @@
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr"/>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>dealFilter8 Iced Desserts 冰品點心</t>
-        </is>
-      </c>
-      <c r="AD73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="inlineStr"/>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7,Deal Filter Tag &gt; dealFilter8</t>
+        </is>
+      </c>
       <c r="AE73" t="inlineStr"/>
     </row>
     <row r="74">
@@ -10496,7 +10500,11 @@
       <c r="AA74" t="inlineStr"/>
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="inlineStr"/>
-      <c r="AD74" t="inlineStr"/>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE74" t="inlineStr"/>
     </row>
     <row r="75">
@@ -10595,7 +10603,11 @@
       <c r="AA75" t="inlineStr"/>
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="inlineStr"/>
-      <c r="AD75" t="inlineStr"/>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR</t>
+        </is>
+      </c>
       <c r="AE75" t="inlineStr"/>
     </row>
     <row r="76">
@@ -10753,13 +10765,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
+      <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="inlineStr"/>
-      <c r="AD76" t="inlineStr"/>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7</t>
+        </is>
+      </c>
       <c r="AE76" t="inlineStr"/>
     </row>
     <row r="77">
@@ -10917,17 +10929,13 @@
 - 麥當勞保有解釋、隨時調整活動辦法、活動時間、活動內容、優惠政策及終止活動之權利</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>dealFilter7 Burgers &amp; Chicken 漢堡鷄肉</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>dealFilter8 Iced Desserts 冰品點心</t>
-        </is>
-      </c>
-      <c r="AD77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="inlineStr"/>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter7,Deal Filter Tag &gt; dealFilter8,Deal Filter Tag &gt; dealFilter9</t>
+        </is>
+      </c>
       <c r="AE77" t="inlineStr"/>
     </row>
     <row r="78">
@@ -11036,17 +11044,13 @@
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="inlineStr"/>
       <c r="AA78" t="inlineStr"/>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>dealFilter8 Iced Desserts 冰品點心</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>dealFilter9McCafe &amp; Drinks 咖啡飲品</t>
-        </is>
-      </c>
-      <c r="AD78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="inlineStr"/>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>Claim Type &gt; Scan And Go QR,Deal Filter Tag &gt; dealFilter8,Deal Filter Tag &gt; dealFilter9</t>
+        </is>
+      </c>
       <c r="AE78" t="inlineStr"/>
     </row>
   </sheetData>
